--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>37336</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>37336</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>37336</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>37336</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37336</v>
+        <v>49379</v>
       </c>
       <c r="C2" t="n">
-        <v>37336</v>
+        <v>49379</v>
       </c>
       <c r="D2" t="n">
-        <v>37336</v>
+        <v>49379</v>
       </c>
       <c r="E2" t="n">
-        <v>37336</v>
+        <v>49379</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49379</v>
+        <v>48928</v>
       </c>
       <c r="C2" t="n">
-        <v>49379</v>
+        <v>48928</v>
       </c>
       <c r="D2" t="n">
-        <v>49379</v>
+        <v>48928</v>
       </c>
       <c r="E2" t="n">
-        <v>49379</v>
+        <v>48928</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48928</v>
+        <v>54655</v>
       </c>
       <c r="C2" t="n">
-        <v>48928</v>
+        <v>63</v>
       </c>
       <c r="D2" t="n">
-        <v>48928</v>
+        <v>63</v>
       </c>
       <c r="E2" t="n">
-        <v>48928</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54655</v>
+        <v>71290</v>
       </c>
       <c r="C2" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71290</v>
+        <v>71277</v>
       </c>
       <c r="C2" t="n">
-        <v>50</v>
+        <v>1516</v>
       </c>
       <c r="D2" t="n">
-        <v>50</v>
+        <v>1516</v>
       </c>
       <c r="E2" t="n">
-        <v>50</v>
+        <v>1516</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71277</v>
+        <v>71371</v>
       </c>
       <c r="C2" t="n">
-        <v>1516</v>
+        <v>3033</v>
       </c>
       <c r="D2" t="n">
-        <v>1516</v>
+        <v>3033</v>
       </c>
       <c r="E2" t="n">
-        <v>1516</v>
+        <v>3033</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71371</v>
+        <v>71279</v>
       </c>
       <c r="C2" t="n">
-        <v>3033</v>
+        <v>1483</v>
       </c>
       <c r="D2" t="n">
-        <v>3033</v>
+        <v>1483</v>
       </c>
       <c r="E2" t="n">
-        <v>3033</v>
+        <v>1483</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71279</v>
+        <v>71325</v>
       </c>
       <c r="C2" t="n">
-        <v>1483</v>
+        <v>1589</v>
       </c>
       <c r="D2" t="n">
-        <v>1483</v>
+        <v>1571</v>
       </c>
       <c r="E2" t="n">
-        <v>1483</v>
+        <v>1589</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71325</v>
+        <v>71347</v>
       </c>
       <c r="C2" t="n">
-        <v>1589</v>
+        <v>1473</v>
       </c>
       <c r="D2" t="n">
-        <v>1571</v>
+        <v>1404</v>
       </c>
       <c r="E2" t="n">
-        <v>1589</v>
+        <v>1473</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71347</v>
+        <v>64197</v>
       </c>
       <c r="C2" t="n">
-        <v>1473</v>
+        <v>866</v>
       </c>
       <c r="D2" t="n">
-        <v>1404</v>
+        <v>594</v>
       </c>
       <c r="E2" t="n">
-        <v>1473</v>
+        <v>866</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -446,20 +446,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>google.com</t>
+          <t>github.com</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64197</v>
+        <v>41168</v>
       </c>
       <c r="C2" t="n">
-        <v>866</v>
+        <v>127</v>
       </c>
       <c r="D2" t="n">
-        <v>594</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
-        <v>866</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41168</v>
+        <v>41126</v>
       </c>
       <c r="C2" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="E2" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41126</v>
+        <v>4</v>
       </c>
       <c r="C2" t="n">
-        <v>124</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>124</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -450,16 +450,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>41165</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>141</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,25 +429,55 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>generated_at</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>subdomains_count</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>live_hosts_count</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>dead_hosts_count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ports_count</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>technologies_count</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>subdomains</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>live_hosts</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>dead_hosts</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ports</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>technologies</t>
         </is>
@@ -459,20 +489,50 @@
           <t>example.com</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>2</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-08-03 15:40:11 UTC</t>
+        </is>
       </c>
       <c r="C2" t="n">
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>api.example.com; www.example.com</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://example.com; https://api.example.com</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://dead.example.com</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>https://example.com:443 (https)</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://example.com: HTTPX: HTML5 | Webanalyze: nginx</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -569,7 +629,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{'host': 'https://example.com', 'port': '443', 'service': 'https'}</t>
+          <t>https://dead.example.com</t>
         </is>
       </c>
     </row>
@@ -579,6 +639,54 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>host</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>port</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>service</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>https://example.com</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>443</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -614,32 +722,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>reports</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>/Users/sohampatil/.vscode/tmp/tmp_vscode_2/pytest-of-sohampatil/pytest-25/test_generate_excel_report_cre0/reports/report.xlsx</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/reports/report.xlsx
+++ b/reports/report.xlsx
@@ -667,7 +667,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>http://www.www.tmail.pk</t>
+          <t>http://mail.www.tmail.pk</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr"/>
@@ -677,7 +677,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>http://www.tmail.pk</t>
+          <t>http://www.www.tmail.pk</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr"/>
@@ -687,7 +687,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>http://mail.www.tmail.pk</t>
+          <t>http://www.tmail.pk</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr"/>
@@ -792,7 +792,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>http://www.www.tmail.pk</t>
+          <t>http://mail.www.tmail.pk</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>http://www.tmail.pk</t>
+          <t>http://www.www.tmail.pk</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>http://mail.www.tmail.pk</t>
+          <t>http://www.tmail.pk</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>www.www.tmail.pk</t>
+          <t>mail.www.tmail.pk</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>www.tmail.pk</t>
+          <t>www.www.tmail.pk</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>mail.www.tmail.pk</t>
+          <t>www.tmail.pk</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
